--- a/Excel/SkillWeaponConfig.xlsx
+++ b/Excel/SkillWeaponConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{296AA41A-646E-4B2A-B4A7-97E5DEE5EB47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4F3DFA-0837-4B24-AAC9-931E15EE5F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillWeaponConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="29">
   <si>
     <t>Id</t>
   </si>
@@ -517,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:J114"/>
+  <dimension ref="C1:J117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
@@ -844,19 +844,19 @@
     </row>
     <row r="15" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C15" s="1">
-        <v>51011101</v>
+        <v>50000501</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="1">
-        <v>61012101</v>
+        <v>60000101</v>
       </c>
       <c r="F15" s="1">
-        <v>61012101</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>61011101</v>
+        <v>60000101</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -865,24 +865,24 @@
         <v>0</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>60000501</v>
       </c>
     </row>
     <row r="16" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C16" s="1">
-        <v>51011102</v>
+        <v>50000502</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E16" s="1">
-        <v>61012102</v>
+        <v>60000102</v>
       </c>
       <c r="F16" s="1">
-        <v>61012102</v>
+        <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>61011102</v>
+        <v>60000102</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -891,24 +891,24 @@
         <v>0</v>
       </c>
       <c r="J16" s="1">
-        <v>0</v>
+        <v>60000501</v>
       </c>
     </row>
     <row r="17" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C17" s="1">
-        <v>51011103</v>
+        <v>50000503</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="1">
-        <v>61012103</v>
+        <v>60000103</v>
       </c>
       <c r="F17" s="1">
-        <v>61012103</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>61011103</v>
+        <v>60000103</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>
@@ -917,24 +917,24 @@
         <v>0</v>
       </c>
       <c r="J17" s="1">
-        <v>0</v>
+        <v>60000502</v>
       </c>
     </row>
     <row r="18" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C18" s="1">
-        <v>51011104</v>
+        <v>51011101</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="1">
-        <v>61012104</v>
+        <v>61012101</v>
       </c>
       <c r="F18" s="1">
-        <v>61012104</v>
+        <v>61012101</v>
       </c>
       <c r="G18" s="1">
-        <v>61011104</v>
+        <v>61011101</v>
       </c>
       <c r="H18" s="1">
         <v>0</v>
@@ -948,19 +948,19 @@
     </row>
     <row r="19" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C19" s="1">
-        <v>51011105</v>
+        <v>51011102</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="1">
-        <v>61012105</v>
+        <v>61012102</v>
       </c>
       <c r="F19" s="1">
-        <v>61012105</v>
+        <v>61012102</v>
       </c>
       <c r="G19" s="1">
-        <v>61011105</v>
+        <v>61011102</v>
       </c>
       <c r="H19" s="1">
         <v>0</v>
@@ -974,19 +974,19 @@
     </row>
     <row r="20" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C20" s="1">
-        <v>51011106</v>
+        <v>51011103</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="1">
-        <v>61012106</v>
+        <v>61012103</v>
       </c>
       <c r="F20" s="1">
-        <v>61012106</v>
+        <v>61012103</v>
       </c>
       <c r="G20" s="1">
-        <v>61011106</v>
+        <v>61011103</v>
       </c>
       <c r="H20" s="1">
         <v>0</v>
@@ -1000,19 +1000,19 @@
     </row>
     <row r="21" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C21" s="1">
-        <v>51011201</v>
+        <v>51011104</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="1">
-        <v>61012201</v>
+        <v>61012104</v>
       </c>
       <c r="F21" s="1">
-        <v>61012201</v>
+        <v>61012104</v>
       </c>
       <c r="G21" s="1">
-        <v>61011201</v>
+        <v>61011104</v>
       </c>
       <c r="H21" s="1">
         <v>0</v>
@@ -1026,19 +1026,19 @@
     </row>
     <row r="22" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C22" s="1">
-        <v>51011202</v>
+        <v>51011105</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E22" s="1">
-        <v>61012202</v>
+        <v>61012105</v>
       </c>
       <c r="F22" s="1">
-        <v>61012202</v>
+        <v>61012105</v>
       </c>
       <c r="G22" s="1">
-        <v>61011202</v>
+        <v>61011105</v>
       </c>
       <c r="H22" s="1">
         <v>0</v>
@@ -1052,19 +1052,19 @@
     </row>
     <row r="23" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C23" s="1">
-        <v>51011203</v>
+        <v>51011106</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E23" s="1">
-        <v>61012203</v>
+        <v>61012106</v>
       </c>
       <c r="F23" s="1">
-        <v>61012203</v>
+        <v>61012106</v>
       </c>
       <c r="G23" s="1">
-        <v>61011203</v>
+        <v>61011106</v>
       </c>
       <c r="H23" s="1">
         <v>0</v>
@@ -1078,19 +1078,19 @@
     </row>
     <row r="24" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C24" s="1">
-        <v>51011204</v>
+        <v>51011201</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E24" s="1">
-        <v>61012204</v>
+        <v>61012201</v>
       </c>
       <c r="F24" s="1">
-        <v>61012204</v>
+        <v>61012201</v>
       </c>
       <c r="G24" s="1">
-        <v>61011204</v>
+        <v>61011201</v>
       </c>
       <c r="H24" s="1">
         <v>0</v>
@@ -1102,21 +1102,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C25" s="1">
-        <v>51011205</v>
+        <v>51011202</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E25" s="1">
-        <v>61012205</v>
+        <v>61012202</v>
       </c>
       <c r="F25" s="1">
-        <v>61012205</v>
+        <v>61012202</v>
       </c>
       <c r="G25" s="1">
-        <v>61011205</v>
+        <v>61011202</v>
       </c>
       <c r="H25" s="1">
         <v>0</v>
@@ -1128,21 +1128,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C26" s="1">
-        <v>51011206</v>
+        <v>51011203</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>19</v>
       </c>
       <c r="E26" s="1">
-        <v>61012206</v>
+        <v>61012203</v>
       </c>
       <c r="F26" s="1">
-        <v>61012206</v>
+        <v>61012203</v>
       </c>
       <c r="G26" s="1">
-        <v>61011206</v>
+        <v>61011203</v>
       </c>
       <c r="H26" s="1">
         <v>0</v>
@@ -1156,19 +1156,19 @@
     </row>
     <row r="27" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="1">
-        <v>51011301</v>
+        <v>51011204</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1">
-        <v>61012301</v>
+        <v>61012204</v>
       </c>
       <c r="F27" s="1">
-        <v>61012301</v>
+        <v>61012204</v>
       </c>
       <c r="G27" s="1">
-        <v>61011301</v>
+        <v>61011204</v>
       </c>
       <c r="H27" s="1">
         <v>0</v>
@@ -1180,21 +1180,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C28" s="1">
-        <v>51011302</v>
+        <v>51011205</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1">
-        <v>61012302</v>
+        <v>61012205</v>
       </c>
       <c r="F28" s="1">
-        <v>61012302</v>
+        <v>61012205</v>
       </c>
       <c r="G28" s="1">
-        <v>61011302</v>
+        <v>61011205</v>
       </c>
       <c r="H28" s="1">
         <v>0</v>
@@ -1206,21 +1206,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C29" s="1">
-        <v>51011303</v>
+        <v>51011206</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E29" s="1">
-        <v>61012303</v>
+        <v>61012206</v>
       </c>
       <c r="F29" s="1">
-        <v>61012303</v>
+        <v>61012206</v>
       </c>
       <c r="G29" s="1">
-        <v>61011303</v>
+        <v>61011206</v>
       </c>
       <c r="H29" s="1">
         <v>0</v>
@@ -1234,19 +1234,19 @@
     </row>
     <row r="30" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C30" s="1">
-        <v>51011304</v>
+        <v>51011301</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E30" s="1">
-        <v>61012304</v>
+        <v>61012301</v>
       </c>
       <c r="F30" s="1">
-        <v>61012304</v>
+        <v>61012301</v>
       </c>
       <c r="G30" s="1">
-        <v>61011304</v>
+        <v>61011301</v>
       </c>
       <c r="H30" s="1">
         <v>0</v>
@@ -1258,21 +1258,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C31" s="1">
-        <v>51011305</v>
+        <v>51011302</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E31" s="1">
-        <v>61012305</v>
+        <v>61012302</v>
       </c>
       <c r="F31" s="1">
-        <v>61012305</v>
+        <v>61012302</v>
       </c>
       <c r="G31" s="1">
-        <v>61011305</v>
+        <v>61011302</v>
       </c>
       <c r="H31" s="1">
         <v>0</v>
@@ -1284,21 +1284,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C32" s="1">
-        <v>51011306</v>
+        <v>51011303</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>20</v>
       </c>
       <c r="E32" s="1">
-        <v>61012306</v>
+        <v>61012303</v>
       </c>
       <c r="F32" s="1">
-        <v>61012306</v>
+        <v>61012303</v>
       </c>
       <c r="G32" s="1">
-        <v>61011306</v>
+        <v>61011303</v>
       </c>
       <c r="H32" s="1">
         <v>0</v>
@@ -1310,93 +1310,93 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C33" s="1">
-        <v>52011101</v>
+        <v>51011304</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33" s="1">
-        <v>62011101</v>
+        <v>61012304</v>
       </c>
       <c r="F33" s="1">
-        <v>0</v>
+        <v>61012304</v>
       </c>
       <c r="G33" s="1">
-        <v>0</v>
+        <v>61011304</v>
       </c>
       <c r="H33" s="1">
-        <v>62011101</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1">
-        <v>62011201</v>
+        <v>0</v>
       </c>
       <c r="J33" s="1">
-        <v>62011201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C34" s="1">
-        <v>52011102</v>
+        <v>51011305</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E34" s="1">
-        <v>62011102</v>
+        <v>61012305</v>
       </c>
       <c r="F34" s="1">
-        <v>0</v>
+        <v>61012305</v>
       </c>
       <c r="G34" s="1">
-        <v>0</v>
+        <v>61011305</v>
       </c>
       <c r="H34" s="1">
-        <v>62011102</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1">
-        <v>62011202</v>
+        <v>0</v>
       </c>
       <c r="J34" s="1">
-        <v>62011202</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C35" s="1">
-        <v>52011103</v>
+        <v>51011306</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" s="1">
-        <v>62011103</v>
+        <v>61012306</v>
       </c>
       <c r="F35" s="1">
-        <v>0</v>
+        <v>61012306</v>
       </c>
       <c r="G35" s="1">
-        <v>0</v>
+        <v>61011306</v>
       </c>
       <c r="H35" s="1">
-        <v>62011103</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1">
-        <v>62011203</v>
+        <v>0</v>
       </c>
       <c r="J35" s="1">
-        <v>62011203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C36" s="1">
-        <v>52011104</v>
+        <v>52011101</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E36" s="1">
-        <v>62011104</v>
+        <v>62011101</v>
       </c>
       <c r="F36" s="1">
         <v>0</v>
@@ -1405,24 +1405,24 @@
         <v>0</v>
       </c>
       <c r="H36" s="1">
-        <v>62011104</v>
+        <v>62011101</v>
       </c>
       <c r="I36" s="1">
-        <v>62011204</v>
+        <v>62011201</v>
       </c>
       <c r="J36" s="1">
-        <v>62011204</v>
+        <v>62011201</v>
       </c>
     </row>
     <row r="37" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C37" s="1">
-        <v>52011105</v>
+        <v>52011102</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E37" s="1">
-        <v>62011105</v>
+        <v>62011102</v>
       </c>
       <c r="F37" s="1">
         <v>0</v>
@@ -1431,24 +1431,24 @@
         <v>0</v>
       </c>
       <c r="H37" s="1">
-        <v>62011105</v>
+        <v>62011102</v>
       </c>
       <c r="I37" s="1">
-        <v>62011205</v>
+        <v>62011202</v>
       </c>
       <c r="J37" s="1">
-        <v>62011205</v>
+        <v>62011202</v>
       </c>
     </row>
     <row r="38" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C38" s="1">
-        <v>52011106</v>
+        <v>52011103</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>21</v>
       </c>
       <c r="E38" s="1">
-        <v>62011106</v>
+        <v>62011103</v>
       </c>
       <c r="F38" s="1">
         <v>0</v>
@@ -1457,24 +1457,24 @@
         <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>62011106</v>
+        <v>62011103</v>
       </c>
       <c r="I38" s="1">
-        <v>62011206</v>
+        <v>62011203</v>
       </c>
       <c r="J38" s="1">
-        <v>62011206</v>
+        <v>62011203</v>
       </c>
     </row>
     <row r="39" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C39" s="1">
-        <v>52011201</v>
+        <v>52011104</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E39" s="1">
-        <v>62011301</v>
+        <v>62011104</v>
       </c>
       <c r="F39" s="1">
         <v>0</v>
@@ -1483,24 +1483,24 @@
         <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>62011301</v>
+        <v>62011104</v>
       </c>
       <c r="I39" s="1">
-        <v>62012101</v>
+        <v>62011204</v>
       </c>
       <c r="J39" s="1">
-        <v>62012101</v>
+        <v>62011204</v>
       </c>
     </row>
     <row r="40" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C40" s="1">
-        <v>52011202</v>
+        <v>52011105</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E40" s="1">
-        <v>62011302</v>
+        <v>62011105</v>
       </c>
       <c r="F40" s="1">
         <v>0</v>
@@ -1509,24 +1509,24 @@
         <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>62011302</v>
+        <v>62011105</v>
       </c>
       <c r="I40" s="1">
-        <v>62012102</v>
+        <v>62011205</v>
       </c>
       <c r="J40" s="1">
-        <v>62012102</v>
+        <v>62011205</v>
       </c>
     </row>
     <row r="41" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C41" s="1">
-        <v>52011203</v>
+        <v>52011106</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E41" s="1">
-        <v>62011303</v>
+        <v>62011106</v>
       </c>
       <c r="F41" s="1">
         <v>0</v>
@@ -1535,24 +1535,24 @@
         <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>62011303</v>
+        <v>62011106</v>
       </c>
       <c r="I41" s="1">
-        <v>62012103</v>
+        <v>62011206</v>
       </c>
       <c r="J41" s="1">
-        <v>62012103</v>
+        <v>62011206</v>
       </c>
     </row>
     <row r="42" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C42" s="1">
-        <v>52011204</v>
+        <v>52011201</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E42" s="1">
-        <v>62011304</v>
+        <v>62011301</v>
       </c>
       <c r="F42" s="1">
         <v>0</v>
@@ -1561,24 +1561,24 @@
         <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>62011304</v>
+        <v>62011301</v>
       </c>
       <c r="I42" s="1">
-        <v>62012104</v>
+        <v>62012101</v>
       </c>
       <c r="J42" s="1">
-        <v>62012104</v>
+        <v>62012101</v>
       </c>
     </row>
     <row r="43" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C43" s="1">
-        <v>52011205</v>
+        <v>52011202</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E43" s="1">
-        <v>62011305</v>
+        <v>62011302</v>
       </c>
       <c r="F43" s="1">
         <v>0</v>
@@ -1587,24 +1587,24 @@
         <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>62011305</v>
+        <v>62011302</v>
       </c>
       <c r="I43" s="1">
-        <v>62012105</v>
+        <v>62012102</v>
       </c>
       <c r="J43" s="1">
-        <v>62012105</v>
+        <v>62012102</v>
       </c>
     </row>
     <row r="44" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C44" s="1">
-        <v>52011206</v>
+        <v>52011203</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>22</v>
       </c>
       <c r="E44" s="1">
-        <v>62011306</v>
+        <v>62011303</v>
       </c>
       <c r="F44" s="1">
         <v>0</v>
@@ -1613,24 +1613,24 @@
         <v>0</v>
       </c>
       <c r="H44" s="1">
-        <v>62011306</v>
+        <v>62011303</v>
       </c>
       <c r="I44" s="1">
-        <v>62012106</v>
+        <v>62012103</v>
       </c>
       <c r="J44" s="1">
-        <v>62012106</v>
+        <v>62012103</v>
       </c>
     </row>
     <row r="45" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C45" s="1">
-        <v>52011301</v>
+        <v>52011204</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E45" s="1">
-        <v>62012201</v>
+        <v>62011304</v>
       </c>
       <c r="F45" s="1">
         <v>0</v>
@@ -1639,24 +1639,24 @@
         <v>0</v>
       </c>
       <c r="H45" s="1">
-        <v>62012201</v>
+        <v>62011304</v>
       </c>
       <c r="I45" s="1">
-        <v>62012301</v>
+        <v>62012104</v>
       </c>
       <c r="J45" s="1">
-        <v>62012301</v>
+        <v>62012104</v>
       </c>
     </row>
     <row r="46" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C46" s="1">
-        <v>52011302</v>
+        <v>52011205</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E46" s="1">
-        <v>62012202</v>
+        <v>62011305</v>
       </c>
       <c r="F46" s="1">
         <v>0</v>
@@ -1665,24 +1665,24 @@
         <v>0</v>
       </c>
       <c r="H46" s="1">
-        <v>62012202</v>
+        <v>62011305</v>
       </c>
       <c r="I46" s="1">
-        <v>62012302</v>
+        <v>62012105</v>
       </c>
       <c r="J46" s="1">
-        <v>62012302</v>
+        <v>62012105</v>
       </c>
     </row>
     <row r="47" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C47" s="1">
-        <v>52011303</v>
+        <v>52011206</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E47" s="1">
-        <v>62012203</v>
+        <v>62011306</v>
       </c>
       <c r="F47" s="1">
         <v>0</v>
@@ -1691,24 +1691,24 @@
         <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>62012203</v>
+        <v>62011306</v>
       </c>
       <c r="I47" s="1">
-        <v>62012303</v>
+        <v>62012106</v>
       </c>
       <c r="J47" s="1">
-        <v>62012303</v>
+        <v>62012106</v>
       </c>
     </row>
     <row r="48" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C48" s="1">
-        <v>52011304</v>
+        <v>52011301</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E48" s="1">
-        <v>62012204</v>
+        <v>62012201</v>
       </c>
       <c r="F48" s="1">
         <v>0</v>
@@ -1717,24 +1717,24 @@
         <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>62012204</v>
+        <v>62012201</v>
       </c>
       <c r="I48" s="1">
-        <v>62012304</v>
+        <v>62012301</v>
       </c>
       <c r="J48" s="1">
-        <v>62012304</v>
+        <v>62012301</v>
       </c>
     </row>
     <row r="49" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C49" s="1">
-        <v>52011305</v>
+        <v>52011302</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="1">
-        <v>62012205</v>
+        <v>62012202</v>
       </c>
       <c r="F49" s="1">
         <v>0</v>
@@ -1743,24 +1743,24 @@
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>62012205</v>
+        <v>62012202</v>
       </c>
       <c r="I49" s="1">
-        <v>62012305</v>
+        <v>62012302</v>
       </c>
       <c r="J49" s="1">
-        <v>62012305</v>
+        <v>62012302</v>
       </c>
     </row>
     <row r="50" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C50" s="1">
-        <v>52011306</v>
+        <v>52011303</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E50" s="1">
-        <v>62012206</v>
+        <v>62012203</v>
       </c>
       <c r="F50" s="1">
         <v>0</v>
@@ -1769,105 +1769,105 @@
         <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>62012206</v>
+        <v>62012203</v>
       </c>
       <c r="I50" s="1">
-        <v>62012306</v>
+        <v>62012303</v>
       </c>
       <c r="J50" s="1">
-        <v>62012306</v>
+        <v>62012303</v>
       </c>
     </row>
     <row r="51" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C51" s="1">
-        <v>53011101</v>
+        <v>52011304</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E51" s="1">
-        <v>63011101</v>
+        <v>62012204</v>
       </c>
       <c r="F51" s="1">
-        <v>63011201</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>0</v>
+        <v>62012204</v>
       </c>
       <c r="I51" s="1">
-        <v>0</v>
+        <v>62012304</v>
       </c>
       <c r="J51" s="1">
-        <v>63011101</v>
+        <v>62012304</v>
       </c>
     </row>
     <row r="52" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C52" s="1">
-        <v>53011102</v>
+        <v>52011305</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E52" s="1">
-        <v>63011102</v>
+        <v>62012205</v>
       </c>
       <c r="F52" s="1">
-        <v>63011202</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0</v>
+        <v>62012205</v>
       </c>
       <c r="I52" s="1">
-        <v>0</v>
+        <v>62012305</v>
       </c>
       <c r="J52" s="1">
-        <v>63011102</v>
+        <v>62012305</v>
       </c>
     </row>
     <row r="53" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C53" s="1">
-        <v>53011103</v>
+        <v>52011306</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E53" s="1">
-        <v>63011103</v>
+        <v>62012206</v>
       </c>
       <c r="F53" s="1">
-        <v>63011203</v>
+        <v>0</v>
       </c>
       <c r="G53" s="1">
         <v>0</v>
       </c>
       <c r="H53" s="1">
-        <v>0</v>
+        <v>62012206</v>
       </c>
       <c r="I53" s="1">
-        <v>0</v>
+        <v>62012306</v>
       </c>
       <c r="J53" s="1">
-        <v>63011103</v>
+        <v>62012306</v>
       </c>
     </row>
     <row r="54" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C54" s="1">
-        <v>53011104</v>
+        <v>53011101</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E54" s="1">
-        <v>63011104</v>
+        <v>63011101</v>
       </c>
       <c r="F54" s="1">
-        <v>63011204</v>
+        <v>63011201</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
@@ -1879,21 +1879,21 @@
         <v>0</v>
       </c>
       <c r="J54" s="1">
-        <v>63011104</v>
+        <v>63011101</v>
       </c>
     </row>
     <row r="55" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C55" s="1">
-        <v>53011105</v>
+        <v>53011102</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E55" s="1">
-        <v>63011105</v>
+        <v>63011102</v>
       </c>
       <c r="F55" s="1">
-        <v>63011205</v>
+        <v>63011202</v>
       </c>
       <c r="G55" s="1">
         <v>0</v>
@@ -1905,21 +1905,21 @@
         <v>0</v>
       </c>
       <c r="J55" s="1">
-        <v>63011105</v>
+        <v>63011102</v>
       </c>
     </row>
     <row r="56" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C56" s="1">
-        <v>53011106</v>
+        <v>53011103</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E56" s="1">
-        <v>63011106</v>
+        <v>63011103</v>
       </c>
       <c r="F56" s="1">
-        <v>63011206</v>
+        <v>63011203</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
@@ -1931,21 +1931,21 @@
         <v>0</v>
       </c>
       <c r="J56" s="1">
-        <v>63011106</v>
+        <v>63011103</v>
       </c>
     </row>
     <row r="57" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C57" s="1">
-        <v>53011201</v>
+        <v>53011104</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E57" s="1">
-        <v>63011301</v>
+        <v>63011104</v>
       </c>
       <c r="F57" s="1">
-        <v>63012101</v>
+        <v>63011204</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
@@ -1957,21 +1957,21 @@
         <v>0</v>
       </c>
       <c r="J57" s="1">
-        <v>63011301</v>
+        <v>63011104</v>
       </c>
     </row>
     <row r="58" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C58" s="1">
-        <v>53011202</v>
+        <v>53011105</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E58" s="1">
-        <v>63011302</v>
+        <v>63011105</v>
       </c>
       <c r="F58" s="1">
-        <v>63012102</v>
+        <v>63011205</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
@@ -1983,21 +1983,21 @@
         <v>0</v>
       </c>
       <c r="J58" s="1">
-        <v>63011302</v>
+        <v>63011105</v>
       </c>
     </row>
     <row r="59" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C59" s="1">
-        <v>53011203</v>
+        <v>53011106</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E59" s="1">
-        <v>63011303</v>
+        <v>63011106</v>
       </c>
       <c r="F59" s="1">
-        <v>63012103</v>
+        <v>63011206</v>
       </c>
       <c r="G59" s="1">
         <v>0</v>
@@ -2009,21 +2009,21 @@
         <v>0</v>
       </c>
       <c r="J59" s="1">
-        <v>63011303</v>
+        <v>63011106</v>
       </c>
     </row>
     <row r="60" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C60" s="1">
-        <v>53011204</v>
+        <v>53011201</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E60" s="1">
-        <v>63011304</v>
+        <v>63011301</v>
       </c>
       <c r="F60" s="1">
-        <v>63012104</v>
+        <v>63012101</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
@@ -2035,21 +2035,21 @@
         <v>0</v>
       </c>
       <c r="J60" s="1">
-        <v>63011304</v>
+        <v>63011301</v>
       </c>
     </row>
     <row r="61" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C61" s="1">
-        <v>53011205</v>
+        <v>53011202</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E61" s="1">
-        <v>63011305</v>
+        <v>63011302</v>
       </c>
       <c r="F61" s="1">
-        <v>63012105</v>
+        <v>63012102</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
@@ -2061,21 +2061,21 @@
         <v>0</v>
       </c>
       <c r="J61" s="1">
-        <v>63011305</v>
+        <v>63011302</v>
       </c>
     </row>
     <row r="62" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C62" s="1">
-        <v>53011206</v>
+        <v>53011203</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>25</v>
       </c>
       <c r="E62" s="1">
-        <v>63011306</v>
+        <v>63011303</v>
       </c>
       <c r="F62" s="1">
-        <v>63012106</v>
+        <v>63012103</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
@@ -2087,21 +2087,21 @@
         <v>0</v>
       </c>
       <c r="J62" s="1">
-        <v>63011306</v>
+        <v>63011303</v>
       </c>
     </row>
     <row r="63" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C63" s="1">
-        <v>53011301</v>
+        <v>53011204</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E63" s="1">
-        <v>63012201</v>
+        <v>63011304</v>
       </c>
       <c r="F63" s="1">
-        <v>63012301</v>
+        <v>63012104</v>
       </c>
       <c r="G63" s="1">
         <v>0</v>
@@ -2113,21 +2113,21 @@
         <v>0</v>
       </c>
       <c r="J63" s="1">
-        <v>63012201</v>
+        <v>63011304</v>
       </c>
     </row>
     <row r="64" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C64" s="1">
-        <v>53011302</v>
+        <v>53011205</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E64" s="1">
-        <v>63012202</v>
+        <v>63011305</v>
       </c>
       <c r="F64" s="1">
-        <v>63012302</v>
+        <v>63012105</v>
       </c>
       <c r="G64" s="1">
         <v>0</v>
@@ -2139,21 +2139,21 @@
         <v>0</v>
       </c>
       <c r="J64" s="1">
-        <v>63012202</v>
+        <v>63011305</v>
       </c>
     </row>
     <row r="65" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C65" s="1">
-        <v>53011303</v>
+        <v>53011206</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E65" s="1">
-        <v>63012203</v>
+        <v>63011306</v>
       </c>
       <c r="F65" s="1">
-        <v>63012303</v>
+        <v>63012106</v>
       </c>
       <c r="G65" s="1">
         <v>0</v>
@@ -2165,21 +2165,21 @@
         <v>0</v>
       </c>
       <c r="J65" s="1">
-        <v>63012203</v>
+        <v>63011306</v>
       </c>
     </row>
     <row r="66" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C66" s="1">
-        <v>53011304</v>
+        <v>53011301</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E66" s="1">
-        <v>63012204</v>
+        <v>63012201</v>
       </c>
       <c r="F66" s="1">
-        <v>63012304</v>
+        <v>63012301</v>
       </c>
       <c r="G66" s="1">
         <v>0</v>
@@ -2191,21 +2191,21 @@
         <v>0</v>
       </c>
       <c r="J66" s="1">
-        <v>63012204</v>
+        <v>63012201</v>
       </c>
     </row>
     <row r="67" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C67" s="1">
-        <v>53011305</v>
+        <v>53011302</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E67" s="1">
-        <v>63012205</v>
+        <v>63012202</v>
       </c>
       <c r="F67" s="1">
-        <v>63012305</v>
+        <v>63012302</v>
       </c>
       <c r="G67" s="1">
         <v>0</v>
@@ -2217,21 +2217,21 @@
         <v>0</v>
       </c>
       <c r="J67" s="1">
-        <v>63012205</v>
+        <v>63012202</v>
       </c>
     </row>
     <row r="68" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C68" s="1">
-        <v>53011306</v>
+        <v>53011303</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E68" s="1">
-        <v>63012206</v>
+        <v>63012203</v>
       </c>
       <c r="F68" s="1">
-        <v>63012306</v>
+        <v>63012303</v>
       </c>
       <c r="G68" s="1">
         <v>0</v>
@@ -2243,108 +2243,108 @@
         <v>0</v>
       </c>
       <c r="J68" s="1">
-        <v>63012206</v>
+        <v>63012203</v>
       </c>
     </row>
     <row r="69" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C69" s="1">
-        <v>54011101</v>
+        <v>53011304</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E69" s="4">
-        <v>64011101</v>
+        <v>23</v>
+      </c>
+      <c r="E69" s="1">
+        <v>63012204</v>
       </c>
       <c r="F69" s="1">
-        <v>63011201</v>
+        <v>63012304</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
-      <c r="H69" s="4">
-        <v>64011101</v>
-      </c>
-      <c r="I69" s="5">
-        <v>64012101</v>
+      <c r="H69" s="1">
+        <v>0</v>
+      </c>
+      <c r="I69" s="1">
+        <v>0</v>
       </c>
       <c r="J69" s="1">
-        <v>0</v>
+        <v>63012204</v>
       </c>
     </row>
     <row r="70" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C70" s="1">
-        <v>54011102</v>
+        <v>53011305</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E70" s="4">
-        <v>64011102</v>
+        <v>23</v>
+      </c>
+      <c r="E70" s="1">
+        <v>63012205</v>
       </c>
       <c r="F70" s="1">
-        <v>63011202</v>
+        <v>63012305</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
-      <c r="H70" s="4">
-        <v>64011102</v>
-      </c>
-      <c r="I70" s="5">
-        <v>64012102</v>
+      <c r="H70" s="1">
+        <v>0</v>
+      </c>
+      <c r="I70" s="1">
+        <v>0</v>
       </c>
       <c r="J70" s="1">
-        <v>0</v>
+        <v>63012205</v>
       </c>
     </row>
     <row r="71" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C71" s="1">
-        <v>54011103</v>
+        <v>53011306</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E71" s="4">
-        <v>64011103</v>
+        <v>23</v>
+      </c>
+      <c r="E71" s="1">
+        <v>63012206</v>
       </c>
       <c r="F71" s="1">
-        <v>63011203</v>
+        <v>63012306</v>
       </c>
       <c r="G71" s="1">
         <v>0</v>
       </c>
-      <c r="H71" s="4">
-        <v>64011103</v>
-      </c>
-      <c r="I71" s="5">
-        <v>64012103</v>
+      <c r="H71" s="1">
+        <v>0</v>
+      </c>
+      <c r="I71" s="1">
+        <v>0</v>
       </c>
       <c r="J71" s="1">
-        <v>0</v>
+        <v>63012206</v>
       </c>
     </row>
     <row r="72" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C72" s="1">
-        <v>54011104</v>
+        <v>54011101</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E72" s="4">
-        <v>64011104</v>
+        <v>64011101</v>
       </c>
       <c r="F72" s="1">
-        <v>63011204</v>
+        <v>63011201</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="4">
-        <v>64011104</v>
+        <v>64011101</v>
       </c>
       <c r="I72" s="5">
-        <v>64012104</v>
+        <v>64012101</v>
       </c>
       <c r="J72" s="1">
         <v>0</v>
@@ -2352,25 +2352,25 @@
     </row>
     <row r="73" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C73" s="1">
-        <v>54011105</v>
+        <v>54011102</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E73" s="4">
-        <v>64011105</v>
+        <v>64011102</v>
       </c>
       <c r="F73" s="1">
-        <v>63011205</v>
+        <v>63011202</v>
       </c>
       <c r="G73" s="1">
         <v>0</v>
       </c>
       <c r="H73" s="4">
-        <v>64011105</v>
+        <v>64011102</v>
       </c>
       <c r="I73" s="5">
-        <v>64012105</v>
+        <v>64012102</v>
       </c>
       <c r="J73" s="1">
         <v>0</v>
@@ -2378,25 +2378,25 @@
     </row>
     <row r="74" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C74" s="1">
-        <v>54011106</v>
+        <v>54011103</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>26</v>
       </c>
       <c r="E74" s="4">
-        <v>64011106</v>
+        <v>64011103</v>
       </c>
       <c r="F74" s="1">
-        <v>63011206</v>
+        <v>63011203</v>
       </c>
       <c r="G74" s="1">
         <v>0</v>
       </c>
       <c r="H74" s="4">
-        <v>64011106</v>
+        <v>64011103</v>
       </c>
       <c r="I74" s="5">
-        <v>64012106</v>
+        <v>64012103</v>
       </c>
       <c r="J74" s="1">
         <v>0</v>
@@ -2404,25 +2404,25 @@
     </row>
     <row r="75" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C75" s="1">
-        <v>54011201</v>
+        <v>54011104</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E75" s="5">
-        <v>64011201</v>
+        <v>26</v>
+      </c>
+      <c r="E75" s="4">
+        <v>64011104</v>
       </c>
       <c r="F75" s="1">
-        <v>63012101</v>
+        <v>63011204</v>
       </c>
       <c r="G75" s="1">
         <v>0</v>
       </c>
-      <c r="H75" s="5">
-        <v>64011201</v>
-      </c>
-      <c r="I75" s="4">
-        <v>64012201</v>
+      <c r="H75" s="4">
+        <v>64011104</v>
+      </c>
+      <c r="I75" s="5">
+        <v>64012104</v>
       </c>
       <c r="J75" s="1">
         <v>0</v>
@@ -2430,25 +2430,25 @@
     </row>
     <row r="76" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C76" s="1">
-        <v>54011202</v>
+        <v>54011105</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E76" s="5">
-        <v>64011202</v>
+        <v>26</v>
+      </c>
+      <c r="E76" s="4">
+        <v>64011105</v>
       </c>
       <c r="F76" s="1">
-        <v>63012102</v>
+        <v>63011205</v>
       </c>
       <c r="G76" s="1">
         <v>0</v>
       </c>
-      <c r="H76" s="5">
-        <v>64011202</v>
-      </c>
-      <c r="I76" s="4">
-        <v>64012202</v>
+      <c r="H76" s="4">
+        <v>64011105</v>
+      </c>
+      <c r="I76" s="5">
+        <v>64012105</v>
       </c>
       <c r="J76" s="1">
         <v>0</v>
@@ -2456,25 +2456,25 @@
     </row>
     <row r="77" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C77" s="1">
-        <v>54011203</v>
+        <v>54011106</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E77" s="5">
-        <v>64011203</v>
+        <v>26</v>
+      </c>
+      <c r="E77" s="4">
+        <v>64011106</v>
       </c>
       <c r="F77" s="1">
-        <v>63012103</v>
+        <v>63011206</v>
       </c>
       <c r="G77" s="1">
         <v>0</v>
       </c>
-      <c r="H77" s="5">
-        <v>64011203</v>
-      </c>
-      <c r="I77" s="4">
-        <v>64012203</v>
+      <c r="H77" s="4">
+        <v>64011106</v>
+      </c>
+      <c r="I77" s="5">
+        <v>64012106</v>
       </c>
       <c r="J77" s="1">
         <v>0</v>
@@ -2482,25 +2482,25 @@
     </row>
     <row r="78" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C78" s="1">
-        <v>54011204</v>
+        <v>54011201</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E78" s="5">
-        <v>64011204</v>
+        <v>64011201</v>
       </c>
       <c r="F78" s="1">
-        <v>63012104</v>
+        <v>63012101</v>
       </c>
       <c r="G78" s="1">
         <v>0</v>
       </c>
       <c r="H78" s="5">
-        <v>64011204</v>
+        <v>64011201</v>
       </c>
       <c r="I78" s="4">
-        <v>64012204</v>
+        <v>64012201</v>
       </c>
       <c r="J78" s="1">
         <v>0</v>
@@ -2508,25 +2508,25 @@
     </row>
     <row r="79" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C79" s="1">
-        <v>54011205</v>
+        <v>54011202</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E79" s="5">
-        <v>64011205</v>
+        <v>64011202</v>
       </c>
       <c r="F79" s="1">
-        <v>63012105</v>
+        <v>63012102</v>
       </c>
       <c r="G79" s="1">
         <v>0</v>
       </c>
       <c r="H79" s="5">
-        <v>64011205</v>
+        <v>64011202</v>
       </c>
       <c r="I79" s="4">
-        <v>64012205</v>
+        <v>64012202</v>
       </c>
       <c r="J79" s="1">
         <v>0</v>
@@ -2534,25 +2534,25 @@
     </row>
     <row r="80" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C80" s="1">
-        <v>54011206</v>
+        <v>54011203</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E80" s="5">
-        <v>64011206</v>
+        <v>64011203</v>
       </c>
       <c r="F80" s="1">
-        <v>63012106</v>
+        <v>63012103</v>
       </c>
       <c r="G80" s="1">
         <v>0</v>
       </c>
       <c r="H80" s="5">
-        <v>64011206</v>
+        <v>64011203</v>
       </c>
       <c r="I80" s="4">
-        <v>64012206</v>
+        <v>64012203</v>
       </c>
       <c r="J80" s="1">
         <v>0</v>
@@ -2560,25 +2560,25 @@
     </row>
     <row r="81" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C81" s="1">
-        <v>54011301</v>
+        <v>54011204</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E81" s="4">
-        <v>64011301</v>
+        <v>27</v>
+      </c>
+      <c r="E81" s="5">
+        <v>64011204</v>
       </c>
       <c r="F81" s="1">
-        <v>63012301</v>
+        <v>63012104</v>
       </c>
       <c r="G81" s="1">
         <v>0</v>
       </c>
-      <c r="H81" s="4">
-        <v>64011301</v>
-      </c>
-      <c r="I81" s="5">
-        <v>64012301</v>
+      <c r="H81" s="5">
+        <v>64011204</v>
+      </c>
+      <c r="I81" s="4">
+        <v>64012204</v>
       </c>
       <c r="J81" s="1">
         <v>0</v>
@@ -2586,25 +2586,25 @@
     </row>
     <row r="82" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C82" s="1">
-        <v>54011302</v>
+        <v>54011205</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E82" s="4">
-        <v>64011302</v>
+        <v>27</v>
+      </c>
+      <c r="E82" s="5">
+        <v>64011205</v>
       </c>
       <c r="F82" s="1">
-        <v>63012302</v>
+        <v>63012105</v>
       </c>
       <c r="G82" s="1">
         <v>0</v>
       </c>
-      <c r="H82" s="4">
-        <v>64011302</v>
-      </c>
-      <c r="I82" s="5">
-        <v>64012302</v>
+      <c r="H82" s="5">
+        <v>64011205</v>
+      </c>
+      <c r="I82" s="4">
+        <v>64012205</v>
       </c>
       <c r="J82" s="1">
         <v>0</v>
@@ -2612,25 +2612,25 @@
     </row>
     <row r="83" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C83" s="1">
-        <v>54011303</v>
+        <v>54011206</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E83" s="4">
-        <v>64011303</v>
+        <v>27</v>
+      </c>
+      <c r="E83" s="5">
+        <v>64011206</v>
       </c>
       <c r="F83" s="1">
-        <v>63012303</v>
+        <v>63012106</v>
       </c>
       <c r="G83" s="1">
         <v>0</v>
       </c>
-      <c r="H83" s="4">
-        <v>64011303</v>
-      </c>
-      <c r="I83" s="5">
-        <v>64012303</v>
+      <c r="H83" s="5">
+        <v>64011206</v>
+      </c>
+      <c r="I83" s="4">
+        <v>64012206</v>
       </c>
       <c r="J83" s="1">
         <v>0</v>
@@ -2638,25 +2638,25 @@
     </row>
     <row r="84" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="1">
-        <v>54011304</v>
+        <v>54011301</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E84" s="4">
-        <v>64011304</v>
+        <v>64011301</v>
       </c>
       <c r="F84" s="1">
-        <v>63012304</v>
+        <v>63012301</v>
       </c>
       <c r="G84" s="1">
         <v>0</v>
       </c>
       <c r="H84" s="4">
-        <v>64011304</v>
+        <v>64011301</v>
       </c>
       <c r="I84" s="5">
-        <v>64012304</v>
+        <v>64012301</v>
       </c>
       <c r="J84" s="1">
         <v>0</v>
@@ -2664,25 +2664,25 @@
     </row>
     <row r="85" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="1">
-        <v>54011305</v>
+        <v>54011302</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E85" s="4">
-        <v>64011305</v>
+        <v>64011302</v>
       </c>
       <c r="F85" s="1">
-        <v>63012305</v>
+        <v>63012302</v>
       </c>
       <c r="G85" s="1">
         <v>0</v>
       </c>
       <c r="H85" s="4">
-        <v>64011305</v>
+        <v>64011302</v>
       </c>
       <c r="I85" s="5">
-        <v>64012305</v>
+        <v>64012302</v>
       </c>
       <c r="J85" s="1">
         <v>0</v>
@@ -2690,33 +2690,108 @@
     </row>
     <row r="86" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="1">
-        <v>54011306</v>
+        <v>54011303</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E86" s="4">
+        <v>64011303</v>
+      </c>
+      <c r="F86" s="1">
+        <v>63012303</v>
+      </c>
+      <c r="G86" s="1">
+        <v>0</v>
+      </c>
+      <c r="H86" s="4">
+        <v>64011303</v>
+      </c>
+      <c r="I86" s="5">
+        <v>64012303</v>
+      </c>
+      <c r="J86" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C87" s="1">
+        <v>54011304</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E87" s="4">
+        <v>64011304</v>
+      </c>
+      <c r="F87" s="1">
+        <v>63012304</v>
+      </c>
+      <c r="G87" s="1">
+        <v>0</v>
+      </c>
+      <c r="H87" s="4">
+        <v>64011304</v>
+      </c>
+      <c r="I87" s="5">
+        <v>64012304</v>
+      </c>
+      <c r="J87" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C88" s="1">
+        <v>54011305</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E88" s="4">
+        <v>64011305</v>
+      </c>
+      <c r="F88" s="1">
+        <v>63012305</v>
+      </c>
+      <c r="G88" s="1">
+        <v>0</v>
+      </c>
+      <c r="H88" s="4">
+        <v>64011305</v>
+      </c>
+      <c r="I88" s="5">
+        <v>64012305</v>
+      </c>
+      <c r="J88" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C89" s="1">
+        <v>54011306</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89" s="4">
         <v>64011306</v>
       </c>
-      <c r="F86" s="1">
+      <c r="F89" s="1">
         <v>63012306</v>
       </c>
-      <c r="G86" s="1">
-        <v>0</v>
-      </c>
-      <c r="H86" s="4">
+      <c r="G89" s="1">
+        <v>0</v>
+      </c>
+      <c r="H89" s="4">
         <v>64011306</v>
       </c>
-      <c r="I86" s="5">
+      <c r="I89" s="5">
         <v>64012306</v>
       </c>
-      <c r="J86" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="J89" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="90" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="91" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="92" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2742,6 +2817,9 @@
     <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/SkillWeaponConfig.xlsx
+++ b/Excel/SkillWeaponConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE4F3DFA-0837-4B24-AAC9-931E15EE5F41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1549A-A970-4D5E-8BCE-F71FB04CAA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillWeaponConfig" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="32">
   <si>
     <t>Id</t>
   </si>
@@ -107,6 +107,15 @@
   </si>
   <si>
     <t>黑暗召唤</t>
+  </si>
+  <si>
+    <t>破界巨刃</t>
+  </si>
+  <si>
+    <t>咆哮之击</t>
+  </si>
+  <si>
+    <t>跃空击</t>
   </si>
 </sst>
 </file>
@@ -517,7 +526,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:J117"/>
+  <dimension ref="C1:J116"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
@@ -2792,34 +2801,483 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="90" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C90" s="1">
+        <v>55011101</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E90" s="1">
+        <v>65011101</v>
+      </c>
+      <c r="F90" s="1">
+        <v>0</v>
+      </c>
+      <c r="G90" s="1">
+        <v>65011101</v>
+      </c>
+      <c r="H90" s="1">
+        <v>0</v>
+      </c>
+      <c r="I90" s="1">
+        <v>0</v>
+      </c>
+      <c r="J90" s="1">
+        <v>65012101</v>
+      </c>
+    </row>
+    <row r="91" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C91" s="1">
+        <v>55011102</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E91" s="1">
+        <v>65011102</v>
+      </c>
+      <c r="F91" s="1">
+        <v>0</v>
+      </c>
+      <c r="G91" s="1">
+        <v>65011102</v>
+      </c>
+      <c r="H91" s="1">
+        <v>0</v>
+      </c>
+      <c r="I91" s="1">
+        <v>0</v>
+      </c>
+      <c r="J91" s="1">
+        <v>65012102</v>
+      </c>
+    </row>
+    <row r="92" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C92" s="1">
+        <v>55011103</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E92" s="1">
+        <v>65011103</v>
+      </c>
+      <c r="F92" s="1">
+        <v>0</v>
+      </c>
+      <c r="G92" s="1">
+        <v>65011103</v>
+      </c>
+      <c r="H92" s="1">
+        <v>0</v>
+      </c>
+      <c r="I92" s="1">
+        <v>0</v>
+      </c>
+      <c r="J92" s="1">
+        <v>65012103</v>
+      </c>
+    </row>
+    <row r="93" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C93" s="1">
+        <v>55011104</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E93" s="1">
+        <v>65011104</v>
+      </c>
+      <c r="F93" s="1">
+        <v>0</v>
+      </c>
+      <c r="G93" s="1">
+        <v>65011104</v>
+      </c>
+      <c r="H93" s="1">
+        <v>0</v>
+      </c>
+      <c r="I93" s="1">
+        <v>0</v>
+      </c>
+      <c r="J93" s="1">
+        <v>65012104</v>
+      </c>
+    </row>
+    <row r="94" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C94" s="1">
+        <v>55011105</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E94" s="1">
+        <v>65011105</v>
+      </c>
+      <c r="F94" s="1">
+        <v>0</v>
+      </c>
+      <c r="G94" s="1">
+        <v>65011105</v>
+      </c>
+      <c r="H94" s="1">
+        <v>0</v>
+      </c>
+      <c r="I94" s="1">
+        <v>0</v>
+      </c>
+      <c r="J94" s="1">
+        <v>65012105</v>
+      </c>
+    </row>
+    <row r="95" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C95" s="1">
+        <v>55011106</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E95" s="1">
+        <v>65011106</v>
+      </c>
+      <c r="F95" s="1">
+        <v>0</v>
+      </c>
+      <c r="G95" s="1">
+        <v>65011106</v>
+      </c>
+      <c r="H95" s="1">
+        <v>0</v>
+      </c>
+      <c r="I95" s="1">
+        <v>0</v>
+      </c>
+      <c r="J95" s="1">
+        <v>65012106</v>
+      </c>
+    </row>
+    <row r="96" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C96" s="1">
+        <v>55011201</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E96" s="1">
+        <v>65011201</v>
+      </c>
+      <c r="F96" s="1">
+        <v>0</v>
+      </c>
+      <c r="G96" s="1">
+        <v>65011201</v>
+      </c>
+      <c r="H96" s="1">
+        <v>0</v>
+      </c>
+      <c r="I96" s="1">
+        <v>0</v>
+      </c>
+      <c r="J96" s="1">
+        <v>65012201</v>
+      </c>
+    </row>
+    <row r="97" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C97" s="1">
+        <v>55011202</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E97" s="1">
+        <v>65011202</v>
+      </c>
+      <c r="F97" s="1">
+        <v>0</v>
+      </c>
+      <c r="G97" s="1">
+        <v>65011202</v>
+      </c>
+      <c r="H97" s="1">
+        <v>0</v>
+      </c>
+      <c r="I97" s="1">
+        <v>0</v>
+      </c>
+      <c r="J97" s="1">
+        <v>65012202</v>
+      </c>
+    </row>
+    <row r="98" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C98" s="1">
+        <v>55011203</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E98" s="1">
+        <v>65011203</v>
+      </c>
+      <c r="F98" s="1">
+        <v>0</v>
+      </c>
+      <c r="G98" s="1">
+        <v>65011203</v>
+      </c>
+      <c r="H98" s="1">
+        <v>0</v>
+      </c>
+      <c r="I98" s="1">
+        <v>0</v>
+      </c>
+      <c r="J98" s="1">
+        <v>65012203</v>
+      </c>
+    </row>
+    <row r="99" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C99" s="1">
+        <v>55011204</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E99" s="1">
+        <v>65011204</v>
+      </c>
+      <c r="F99" s="1">
+        <v>0</v>
+      </c>
+      <c r="G99" s="1">
+        <v>65011204</v>
+      </c>
+      <c r="H99" s="1">
+        <v>0</v>
+      </c>
+      <c r="I99" s="1">
+        <v>0</v>
+      </c>
+      <c r="J99" s="1">
+        <v>65012204</v>
+      </c>
+    </row>
+    <row r="100" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C100" s="1">
+        <v>55011205</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E100" s="1">
+        <v>65011205</v>
+      </c>
+      <c r="F100" s="1">
+        <v>0</v>
+      </c>
+      <c r="G100" s="1">
+        <v>65011205</v>
+      </c>
+      <c r="H100" s="1">
+        <v>0</v>
+      </c>
+      <c r="I100" s="1">
+        <v>0</v>
+      </c>
+      <c r="J100" s="1">
+        <v>65012205</v>
+      </c>
+    </row>
+    <row r="101" spans="3:10" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C101" s="1">
+        <v>55011206</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E101" s="1">
+        <v>65011206</v>
+      </c>
+      <c r="F101" s="1">
+        <v>0</v>
+      </c>
+      <c r="G101" s="1">
+        <v>65011206</v>
+      </c>
+      <c r="H101" s="1">
+        <v>0</v>
+      </c>
+      <c r="I101" s="1">
+        <v>0</v>
+      </c>
+      <c r="J101" s="1">
+        <v>65012206</v>
+      </c>
+    </row>
+    <row r="102" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C102" s="1">
+        <v>55011301</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E102" s="1">
+        <v>65011301</v>
+      </c>
+      <c r="F102" s="1">
+        <v>0</v>
+      </c>
+      <c r="G102" s="1">
+        <v>65011301</v>
+      </c>
+      <c r="H102" s="1">
+        <v>0</v>
+      </c>
+      <c r="I102" s="1">
+        <v>0</v>
+      </c>
+      <c r="J102" s="1">
+        <v>65012301</v>
+      </c>
+    </row>
+    <row r="103" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C103" s="1">
+        <v>55011302</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E103" s="1">
+        <v>65011302</v>
+      </c>
+      <c r="F103" s="1">
+        <v>0</v>
+      </c>
+      <c r="G103" s="1">
+        <v>65011302</v>
+      </c>
+      <c r="H103" s="1">
+        <v>0</v>
+      </c>
+      <c r="I103" s="1">
+        <v>0</v>
+      </c>
+      <c r="J103" s="1">
+        <v>65012302</v>
+      </c>
+    </row>
+    <row r="104" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C104" s="1">
+        <v>55011303</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E104" s="1">
+        <v>65011303</v>
+      </c>
+      <c r="F104" s="1">
+        <v>0</v>
+      </c>
+      <c r="G104" s="1">
+        <v>65011303</v>
+      </c>
+      <c r="H104" s="1">
+        <v>0</v>
+      </c>
+      <c r="I104" s="1">
+        <v>0</v>
+      </c>
+      <c r="J104" s="1">
+        <v>65012303</v>
+      </c>
+    </row>
+    <row r="105" spans="3:10" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C105" s="1">
+        <v>55011304</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E105" s="1">
+        <v>65011304</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" s="1">
+        <v>65011304</v>
+      </c>
+      <c r="H105" s="1">
+        <v>0</v>
+      </c>
+      <c r="I105" s="1">
+        <v>0</v>
+      </c>
+      <c r="J105" s="1">
+        <v>65012304</v>
+      </c>
+    </row>
+    <row r="106" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C106" s="1">
+        <v>55011305</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E106" s="1">
+        <v>65011305</v>
+      </c>
+      <c r="F106" s="1">
+        <v>0</v>
+      </c>
+      <c r="G106" s="1">
+        <v>65011305</v>
+      </c>
+      <c r="H106" s="1">
+        <v>0</v>
+      </c>
+      <c r="I106" s="1">
+        <v>0</v>
+      </c>
+      <c r="J106" s="1">
+        <v>65012305</v>
+      </c>
+    </row>
+    <row r="107" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C107" s="1">
+        <v>55011306</v>
+      </c>
+      <c r="D107" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E107" s="1">
+        <v>65011306</v>
+      </c>
+      <c r="F107" s="1">
+        <v>0</v>
+      </c>
+      <c r="G107" s="1">
+        <v>65011306</v>
+      </c>
+      <c r="H107" s="1">
+        <v>0</v>
+      </c>
+      <c r="I107" s="1">
+        <v>0</v>
+      </c>
+      <c r="J107" s="1">
+        <v>65012306</v>
+      </c>
+    </row>
+    <row r="108" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="109" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="110" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="111" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="112" spans="3:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="116" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/SkillWeaponConfig.xlsx
+++ b/Excel/SkillWeaponConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A1549A-A970-4D5E-8BCE-F71FB04CAA3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB29228-28CA-4AE2-BA30-2F1BD627DE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -865,7 +865,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>60000101</v>
+        <v>60000801</v>
       </c>
       <c r="H15" s="1">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="1">
-        <v>60000102</v>
+        <v>60000802</v>
       </c>
       <c r="H16" s="1">
         <v>0</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>60000103</v>
+        <v>60000803</v>
       </c>
       <c r="H17" s="1">
         <v>0</v>

--- a/Excel/SkillWeaponConfig.xlsx
+++ b/Excel/SkillWeaponConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB29228-28CA-4AE2-BA30-2F1BD627DE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3DAB27C-F698-4F7A-88FE-CA94CAB7DF22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SkillWeaponConfig" sheetId="1" r:id="rId1"/>
